--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136481238</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136481238</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136481238</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136481238</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38213-2026 artfynd.xlsx
+++ b/artfynd/A 38213-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136481238</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136481209</v>
       </c>
       <c r="B4" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
